--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,6 +1397,739 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123351286</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539141</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6348632</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123351867</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>539103</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6348700</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123350658</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>539183</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6348627</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123351985</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>539184</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6348697</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123351133</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>539164</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6348618</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123349755</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100631</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>539067</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6348590</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123351927</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>539126</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6348690</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351286</v>
+        <v>123350658</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539141</v>
+        <v>539183</v>
       </c>
       <c r="R8" t="n">
-        <v>6348632</v>
+        <v>6348627</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,11 +1475,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351867</v>
+        <v>123351985</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,25 +1513,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539103</v>
+        <v>539184</v>
       </c>
       <c r="R9" t="n">
-        <v>6348700</v>
+        <v>6348697</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,6 +1577,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123350658</v>
+        <v>123351286</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,13 +1648,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539183</v>
+        <v>539141</v>
       </c>
       <c r="R10" t="n">
-        <v>6348627</v>
+        <v>6348632</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,6 +1684,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351985</v>
+        <v>123351867</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1727,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,13 +1755,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539184</v>
+        <v>539103</v>
       </c>
       <c r="R11" t="n">
-        <v>6348697</v>
+        <v>6348700</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,11 +1791,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1820,7 @@
         <v>123351133</v>
       </c>
       <c r="B12" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123349755</v>
+        <v>123351927</v>
       </c>
       <c r="B13" t="n">
-        <v>100631</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,41 +1935,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539067</v>
+        <v>539126</v>
       </c>
       <c r="R13" t="n">
-        <v>6348590</v>
+        <v>6348690</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351927</v>
+        <v>123349755</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>100634</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,46 +2042,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539126</v>
+        <v>539067</v>
       </c>
       <c r="R14" t="n">
-        <v>6348690</v>
+        <v>6348590</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123350658</v>
+        <v>123351286</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539183</v>
+        <v>539141</v>
       </c>
       <c r="R8" t="n">
-        <v>6348627</v>
+        <v>6348632</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,6 +1475,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123351286</v>
+        <v>123349755</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>100636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,25 +1625,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,13 +1653,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539141</v>
+        <v>539067</v>
       </c>
       <c r="R10" t="n">
-        <v>6348632</v>
+        <v>6348590</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,11 +1689,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1718,7 @@
         <v>123351867</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351133</v>
+        <v>123350658</v>
       </c>
       <c r="B12" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,42 +1829,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539164</v>
+        <v>539183</v>
       </c>
       <c r="R12" t="n">
-        <v>6348618</v>
+        <v>6348627</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2030,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123349755</v>
+        <v>123351133</v>
       </c>
       <c r="B14" t="n">
-        <v>100634</v>
+        <v>105476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,34 +2042,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539067</v>
+        <v>539164</v>
       </c>
       <c r="R14" t="n">
-        <v>6348590</v>
+        <v>6348618</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,7 +1399,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351286</v>
+        <v>123351985</v>
       </c>
       <c r="B8" t="n">
         <v>57497</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539141</v>
+        <v>539184</v>
       </c>
       <c r="R8" t="n">
-        <v>6348632</v>
+        <v>6348697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351985</v>
+        <v>123351133</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>105482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,41 +1518,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539184</v>
+        <v>539164</v>
       </c>
       <c r="R9" t="n">
-        <v>6348697</v>
+        <v>6348618</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,11 +1586,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123349755</v>
+        <v>123351867</v>
       </c>
       <c r="B10" t="n">
-        <v>100636</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,25 +1624,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539067</v>
+        <v>539103</v>
       </c>
       <c r="R10" t="n">
-        <v>6348590</v>
+        <v>6348700</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1715,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351867</v>
+        <v>123351286</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,25 +1726,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,13 +1754,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539103</v>
+        <v>539141</v>
       </c>
       <c r="R11" t="n">
-        <v>6348700</v>
+        <v>6348632</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1791,6 +1790,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123350658</v>
+        <v>123351927</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,41 +1833,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539183</v>
+        <v>539126</v>
       </c>
       <c r="R12" t="n">
-        <v>6348627</v>
+        <v>6348690</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351927</v>
+        <v>123350658</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,46 +1940,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539126</v>
+        <v>539183</v>
       </c>
       <c r="R13" t="n">
-        <v>6348690</v>
+        <v>6348627</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351133</v>
+        <v>123349755</v>
       </c>
       <c r="B14" t="n">
-        <v>105476</v>
+        <v>100642</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,38 +2046,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539164</v>
+        <v>539067</v>
       </c>
       <c r="R14" t="n">
-        <v>6348618</v>
+        <v>6348590</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351286</v>
+        <v>123351867</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539141</v>
+        <v>539103</v>
       </c>
       <c r="R8" t="n">
-        <v>6348632</v>
+        <v>6348700</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,11 +1475,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351985</v>
+        <v>123349755</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>100662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,25 +1513,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539184</v>
+        <v>539067</v>
       </c>
       <c r="R9" t="n">
-        <v>6348697</v>
+        <v>6348590</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,11 +1577,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123349755</v>
+        <v>123351286</v>
       </c>
       <c r="B10" t="n">
-        <v>100645</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,25 +1615,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,13 +1643,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539067</v>
+        <v>539141</v>
       </c>
       <c r="R10" t="n">
-        <v>6348590</v>
+        <v>6348632</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,6 +1679,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123350658</v>
+        <v>123351985</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,13 +1750,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539183</v>
+        <v>539184</v>
       </c>
       <c r="R11" t="n">
-        <v>6348627</v>
+        <v>6348697</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1791,6 +1786,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351867</v>
+        <v>123351133</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,38 +1829,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539103</v>
+        <v>539164</v>
       </c>
       <c r="R12" t="n">
-        <v>6348700</v>
+        <v>6348618</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1919,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351927</v>
+        <v>123350658</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,46 +1935,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539126</v>
+        <v>539183</v>
       </c>
       <c r="R13" t="n">
-        <v>6348690</v>
+        <v>6348627</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351133</v>
+        <v>123351927</v>
       </c>
       <c r="B14" t="n">
-        <v>105485</v>
+        <v>57640</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,30 +2037,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539164</v>
+        <v>539126</v>
       </c>
       <c r="R14" t="n">
-        <v>6348618</v>
+        <v>6348690</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351867</v>
+        <v>123351927</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,41 +1411,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539103</v>
+        <v>539126</v>
       </c>
       <c r="R8" t="n">
-        <v>6348700</v>
+        <v>6348690</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123349755</v>
+        <v>123351133</v>
       </c>
       <c r="B9" t="n">
-        <v>100662</v>
+        <v>105518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,34 +1522,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539067</v>
+        <v>539164</v>
       </c>
       <c r="R9" t="n">
-        <v>6348590</v>
+        <v>6348618</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1603,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123351286</v>
+        <v>123350658</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1624,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,13 +1652,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539141</v>
+        <v>539183</v>
       </c>
       <c r="R10" t="n">
-        <v>6348632</v>
+        <v>6348627</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,11 +1688,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351985</v>
+        <v>123351867</v>
       </c>
       <c r="B11" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1726,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,13 +1754,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539184</v>
+        <v>539103</v>
       </c>
       <c r="R11" t="n">
-        <v>6348697</v>
+        <v>6348700</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,11 +1790,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351133</v>
+        <v>123351985</v>
       </c>
       <c r="B12" t="n">
-        <v>105502</v>
+        <v>57506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,45 +1828,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539164</v>
+        <v>539184</v>
       </c>
       <c r="R12" t="n">
-        <v>6348618</v>
+        <v>6348697</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,6 +1892,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123350658</v>
+        <v>123349755</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539183</v>
+        <v>539067</v>
       </c>
       <c r="R13" t="n">
-        <v>6348627</v>
+        <v>6348590</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351927</v>
+        <v>123351286</v>
       </c>
       <c r="B14" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,42 +2041,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539126</v>
+        <v>539141</v>
       </c>
       <c r="R14" t="n">
-        <v>6348690</v>
+        <v>6348632</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,6 +2101,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351927</v>
+        <v>123351286</v>
       </c>
       <c r="B8" t="n">
-        <v>57643</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,42 +1415,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539126</v>
+        <v>539141</v>
       </c>
       <c r="R8" t="n">
-        <v>6348690</v>
+        <v>6348632</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,6 +1475,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351133</v>
+        <v>123351985</v>
       </c>
       <c r="B9" t="n">
-        <v>105518</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,45 +1518,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539164</v>
+        <v>539184</v>
       </c>
       <c r="R9" t="n">
-        <v>6348618</v>
+        <v>6348697</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,6 +1582,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,7 +1616,7 @@
         <v>123350658</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1717,7 +1718,7 @@
         <v>123351867</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1816,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351985</v>
+        <v>123351133</v>
       </c>
       <c r="B12" t="n">
-        <v>57506</v>
+        <v>105520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,41 +1829,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539184</v>
+        <v>539164</v>
       </c>
       <c r="R12" t="n">
-        <v>6348697</v>
+        <v>6348618</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,11 +1897,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,7 +1926,7 @@
         <v>123349755</v>
       </c>
       <c r="B13" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351286</v>
+        <v>123351927</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>57644</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,37 +2041,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539141</v>
+        <v>539126</v>
       </c>
       <c r="R14" t="n">
-        <v>6348632</v>
+        <v>6348690</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,11 +2106,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351286</v>
+        <v>123351927</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,37 +1415,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539141</v>
+        <v>539126</v>
       </c>
       <c r="R8" t="n">
-        <v>6348632</v>
+        <v>6348690</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,11 +1480,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351985</v>
+        <v>123351867</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539184</v>
+        <v>539103</v>
       </c>
       <c r="R9" t="n">
-        <v>6348697</v>
+        <v>6348700</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,11 +1582,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123350658</v>
+        <v>123349755</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,25 +1620,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539183</v>
+        <v>539067</v>
       </c>
       <c r="R10" t="n">
-        <v>6348627</v>
+        <v>6348590</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351867</v>
+        <v>123351133</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,38 +1722,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539103</v>
+        <v>539164</v>
       </c>
       <c r="R11" t="n">
-        <v>6348700</v>
+        <v>6348618</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1817,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351133</v>
+        <v>123351286</v>
       </c>
       <c r="B12" t="n">
-        <v>105520</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,45 +1828,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539164</v>
+        <v>539141</v>
       </c>
       <c r="R12" t="n">
-        <v>6348618</v>
+        <v>6348632</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,6 +1892,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123349755</v>
+        <v>123351985</v>
       </c>
       <c r="B13" t="n">
-        <v>100682</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539067</v>
+        <v>539184</v>
       </c>
       <c r="R13" t="n">
-        <v>6348590</v>
+        <v>6348697</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,6 +1999,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351927</v>
+        <v>123350658</v>
       </c>
       <c r="B14" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,46 +2042,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539126</v>
+        <v>539183</v>
       </c>
       <c r="R14" t="n">
-        <v>6348690</v>
+        <v>6348627</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351927</v>
+        <v>123350658</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,46 +1411,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539126</v>
+        <v>539183</v>
       </c>
       <c r="R8" t="n">
-        <v>6348690</v>
+        <v>6348627</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351867</v>
+        <v>123351133</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,38 +1513,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539103</v>
+        <v>539164</v>
       </c>
       <c r="R9" t="n">
-        <v>6348700</v>
+        <v>6348618</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1710,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351133</v>
+        <v>123351985</v>
       </c>
       <c r="B11" t="n">
-        <v>105095</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,45 +1721,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539164</v>
+        <v>539184</v>
       </c>
       <c r="R11" t="n">
-        <v>6348618</v>
+        <v>6348697</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,6 +1785,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351286</v>
+        <v>123351867</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,25 +1828,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539141</v>
+        <v>539103</v>
       </c>
       <c r="R12" t="n">
-        <v>6348632</v>
+        <v>6348700</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,11 +1892,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351985</v>
+        <v>123351927</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,37 +1934,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539184</v>
+        <v>539126</v>
       </c>
       <c r="R13" t="n">
-        <v>6348697</v>
+        <v>6348690</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,11 +1999,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123350658</v>
+        <v>123351286</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,25 +2037,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2070,13 +2065,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539183</v>
+        <v>539141</v>
       </c>
       <c r="R14" t="n">
-        <v>6348627</v>
+        <v>6348632</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,6 +2101,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123350658</v>
+        <v>123351985</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539183</v>
+        <v>539184</v>
       </c>
       <c r="R8" t="n">
-        <v>6348627</v>
+        <v>6348697</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,6 +1475,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351133</v>
+        <v>123351927</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,30 +1518,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1545,13 +1551,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539164</v>
+        <v>539126</v>
       </c>
       <c r="R9" t="n">
-        <v>6348618</v>
+        <v>6348690</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123349755</v>
+        <v>123351867</v>
       </c>
       <c r="B10" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,25 +1625,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539067</v>
+        <v>539103</v>
       </c>
       <c r="R10" t="n">
-        <v>6348590</v>
+        <v>6348700</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351985</v>
+        <v>123349755</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1727,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,13 +1755,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539184</v>
+        <v>539067</v>
       </c>
       <c r="R11" t="n">
-        <v>6348697</v>
+        <v>6348590</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,11 +1791,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351867</v>
+        <v>123351286</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,25 +1829,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,13 +1857,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539103</v>
+        <v>539141</v>
       </c>
       <c r="R12" t="n">
-        <v>6348700</v>
+        <v>6348632</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,6 +1893,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351927</v>
+        <v>123351133</v>
       </c>
       <c r="B13" t="n">
-        <v>57644</v>
+        <v>105095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,31 +1936,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1963,13 +1968,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539126</v>
+        <v>539164</v>
       </c>
       <c r="R13" t="n">
-        <v>6348690</v>
+        <v>6348618</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351286</v>
+        <v>123350658</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,25 +2042,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539141</v>
+        <v>539183</v>
       </c>
       <c r="R14" t="n">
-        <v>6348632</v>
+        <v>6348627</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,11 +2106,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123351985</v>
+        <v>123350658</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539184</v>
+        <v>539183</v>
       </c>
       <c r="R8" t="n">
-        <v>6348697</v>
+        <v>6348627</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,11 +1475,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123351867</v>
+        <v>123349755</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,25 +1620,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539103</v>
+        <v>539067</v>
       </c>
       <c r="R10" t="n">
-        <v>6348700</v>
+        <v>6348590</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123349755</v>
+        <v>123351286</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,13 +1750,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539067</v>
+        <v>539141</v>
       </c>
       <c r="R11" t="n">
-        <v>6348590</v>
+        <v>6348632</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1791,6 +1786,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351286</v>
+        <v>123351133</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,41 +1829,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539141</v>
+        <v>539164</v>
       </c>
       <c r="R12" t="n">
-        <v>6348632</v>
+        <v>6348618</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,11 +1897,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351133</v>
+        <v>123351985</v>
       </c>
       <c r="B13" t="n">
-        <v>105095</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,45 +1935,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539164</v>
+        <v>539184</v>
       </c>
       <c r="R13" t="n">
-        <v>6348618</v>
+        <v>6348697</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,6 +1999,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123350658</v>
+        <v>123351867</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539183</v>
+        <v>539103</v>
       </c>
       <c r="R14" t="n">
-        <v>6348627</v>
+        <v>6348700</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123350658</v>
+        <v>123351133</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,38 +1411,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539183</v>
+        <v>539164</v>
       </c>
       <c r="R8" t="n">
-        <v>6348627</v>
+        <v>6348618</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1501,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351927</v>
+        <v>123351867</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,46 +1517,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539126</v>
+        <v>539103</v>
       </c>
       <c r="R9" t="n">
-        <v>6348690</v>
+        <v>6348700</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1608,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123349755</v>
+        <v>123351927</v>
       </c>
       <c r="B10" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,41 +1619,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539067</v>
+        <v>539126</v>
       </c>
       <c r="R10" t="n">
-        <v>6348590</v>
+        <v>6348690</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1710,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351286</v>
+        <v>123351985</v>
       </c>
       <c r="B11" t="n">
         <v>57507</v>
@@ -1750,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539141</v>
+        <v>539184</v>
       </c>
       <c r="R11" t="n">
-        <v>6348632</v>
+        <v>6348697</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351133</v>
+        <v>123349755</v>
       </c>
       <c r="B12" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,38 +1837,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539164</v>
+        <v>539067</v>
       </c>
       <c r="R12" t="n">
-        <v>6348618</v>
+        <v>6348590</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351985</v>
+        <v>123351286</v>
       </c>
       <c r="B13" t="n">
         <v>57507</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539184</v>
+        <v>539141</v>
       </c>
       <c r="R13" t="n">
-        <v>6348697</v>
+        <v>6348632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351867</v>
+        <v>123350658</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539103</v>
+        <v>539183</v>
       </c>
       <c r="R14" t="n">
-        <v>6348700</v>
+        <v>6348627</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86695987</v>
+        <v>98224300</v>
       </c>
       <c r="B2" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nylund, Bösebo, Mörlunda, Sm</t>
+          <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539262.4173547321</v>
+        <v>539151</v>
       </c>
       <c r="R2" t="n">
-        <v>6348682.698482096</v>
+        <v>6348669</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,76 +761,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98223985</v>
+        <v>123351286</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539104.983854814</v>
+        <v>539141</v>
       </c>
       <c r="R3" t="n">
-        <v>6348720.117641021</v>
+        <v>6348632</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +838,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,64 +875,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98224400</v>
+        <v>123351985</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539157.0742077776</v>
+        <v>539184</v>
       </c>
       <c r="R4" t="n">
-        <v>6348653.582179394</v>
+        <v>6348697</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,22 +940,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,15 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98224774</v>
+        <v>123356273</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,39 +988,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539129.5034285043</v>
+        <v>539076</v>
       </c>
       <c r="R5" t="n">
-        <v>6348591.151660697</v>
+        <v>6348738</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,22 +1042,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,54 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98224300</v>
+        <v>123356489</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539150.9671381821</v>
+        <v>539091</v>
       </c>
       <c r="R6" t="n">
-        <v>6348669.200859487</v>
+        <v>6348735</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1144,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,64 +1181,64 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98224538</v>
+        <v>86695987</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Nylund, Bösebo, Mörlunda, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539145.556315462</v>
+        <v>539262</v>
       </c>
       <c r="R7" t="n">
-        <v>6348668.608685952</v>
+        <v>6348683</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,22 +1262,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,65 +1282,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marie Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marie Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123350658</v>
+        <v>123351927</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539183</v>
+        <v>539126</v>
       </c>
       <c r="R8" t="n">
-        <v>6348627</v>
+        <v>6348690</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,53 +1396,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123351286</v>
+        <v>98223985</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539141</v>
+        <v>539106</v>
       </c>
       <c r="R9" t="n">
-        <v>6348632</v>
+        <v>6348720</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,17 +1472,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,53 +1504,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123349755</v>
+        <v>98224149</v>
       </c>
       <c r="B10" t="n">
-        <v>100257</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539067</v>
+        <v>539103</v>
       </c>
       <c r="R10" t="n">
-        <v>6348590</v>
+        <v>6348753</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,12 +1580,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,57 +1612,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123351133</v>
+        <v>98224400</v>
       </c>
       <c r="B11" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539164</v>
+        <v>539157</v>
       </c>
       <c r="R11" t="n">
-        <v>6348618</v>
+        <v>6348653</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,12 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,15 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123351867</v>
+        <v>98224538</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,20 +1748,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539103</v>
+        <v>539146</v>
       </c>
       <c r="R12" t="n">
-        <v>6348700</v>
+        <v>6348668</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,12 +1796,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,58 +1828,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123351927</v>
+        <v>123350658</v>
       </c>
       <c r="B13" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539126</v>
+        <v>539183</v>
       </c>
       <c r="R13" t="n">
-        <v>6348690</v>
+        <v>6348627</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,37 +1925,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123351985</v>
+        <v>123351867</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,13 +1960,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539184</v>
+        <v>539103</v>
       </c>
       <c r="R14" t="n">
-        <v>6348697</v>
+        <v>6348700</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,11 +1996,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,6 +2019,499 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123356462</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>539093</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6348741</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101087482</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>539078</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6348617</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123351133</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>539164</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6348618</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>98224774</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>539130</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6348591</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-01-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-01-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123349755</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>539067</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6348590</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37640-2024 artfynd.xlsx
+++ b/artfynd/A 37640-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98224300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351286</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351985</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123356273</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123356489</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86695987</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351927</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98223985</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98224149</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98224400</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98224538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123350658</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351867</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123356462</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2290,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101087482</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351133</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98224774</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,8 +2602,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123349755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>